--- a/outputs/52216.xlsx
+++ b/outputs/52216.xlsx
@@ -368,139 +368,139 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -761,12 +761,12 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="1" width="8.64"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -788,7 +788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -796,7 +796,7 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -804,7 +804,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -812,7 +812,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -820,7 +820,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -854,7 +854,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="8.64"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
@@ -907,7 +907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
@@ -955,7 +955,7 @@
         <v>1779139.76552686</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>13</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
         <v>14</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
         <v>15</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
         <v>16</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>1601225.78897417</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>17</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>983013.733762502</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>19</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>29490.4120128751</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
@@ -1340,12 +1340,12 @@
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1375,28 +1375,28 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="2" t="n">
-        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(1,INDEX((Sheet2!$A$3:$A$20=INPUTS!$A$14)*(Sheet2!$B$3:$B$20=INPUTS!$A16),0),0),MATCH(INPUTS!C$3,Sheet2!$C$1:$G$1,0)),0)</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(INPUTS!$A$14,Sheet2!$A$3:$A$20,0)+1,MATCH(INPUTS!C$3,Sheet2!$C$1:$G$1,0)),0)</f>
         <v>1.24</v>
       </c>
       <c r="D16" s="2" t="n">
-        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(1,INDEX((Sheet2!$A$3:$A$20=INPUTS!$A$14)*(Sheet2!$B$3:$B$20=INPUTS!$A16),0),0),MATCH(INPUTS!D$3,Sheet2!$C$1:$G$1,0)),0)</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(INPUTS!$A$14,Sheet2!$A$3:$A$20,0)+1,MATCH(INPUTS!D$3,Sheet2!$C$1:$G$1,0)),0)</f>
         <v>1.8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(1,INDEX((Sheet2!$A$3:$A$20=INPUTS!$A$14)*(Sheet2!$B$3:$B$20=INPUTS!$A16),0),0),MATCH(INPUTS!E$3,Sheet2!$C$1:$G$1,0)),0)</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(INPUTS!$A$14,Sheet2!$A$3:$A$20,0)+1,MATCH(INPUTS!E$3,Sheet2!$C$1:$G$1,0)),0)</f>
         <v>1.78</v>
       </c>
       <c r="F16" s="2" t="n">
-        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(1,INDEX((Sheet2!$A$3:$A$20=INPUTS!$A$14)*(Sheet2!$B$3:$B$20=INPUTS!$A16),0),0),MATCH(INPUTS!F$3,Sheet2!$C$1:$G$1,0)),0)</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(INPUTS!$A$14,Sheet2!$A$3:$A$20,0)+1,MATCH(INPUTS!F$3,Sheet2!$C$1:$G$1,0)),0)</f>
         <v>1.4</v>
       </c>
       <c r="G16" s="2" t="n">
-        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(1,INDEX((Sheet2!$A$3:$A$20=INPUTS!$A$14)*(Sheet2!$B$3:$B$20=INPUTS!$A16),0),0),MATCH(INPUTS!G$3,Sheet2!$C$1:$G$1,0)),0)</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$C$3:$G$20,MATCH(INPUTS!$A$14,Sheet2!$A$3:$A$20,0)+1,MATCH(INPUTS!G$3,Sheet2!$C$1:$G$1,0)),0)</f>
         <v>1.72</v>
       </c>
       <c r="H16" s="2"/>
@@ -1405,7 +1405,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -1420,7 +1420,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -1450,7 +1450,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1465,7 +1465,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -1480,7 +1480,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -1495,7 +1495,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -1529,7 +1529,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="n">
         <v>1</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
@@ -1775,7 +1775,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="8.64"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G3" s="29"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
         <v>22</v>
       </c>
@@ -1823,7 +1823,7 @@
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
         <v>2</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
         <v>4</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1871,7 +1871,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
         <v>23</v>
       </c>
@@ -1881,7 +1881,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
         <v>2</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
         <v>4</v>
       </c>
@@ -1921,14 +1921,14 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
         <v>24</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
         <v>2</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
         <v>4</v>
       </c>
@@ -1978,14 +1978,14 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="s">
         <v>25</v>
       </c>
@@ -1995,7 +1995,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
         <v>37</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
         <v>4</v>
       </c>
@@ -2035,14 +2035,14 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
         <v>26</v>
       </c>
@@ -2052,7 +2052,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
         <v>2</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
         <v>4</v>
       </c>
@@ -2092,14 +2092,14 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="30" t="s">
         <v>27</v>
       </c>
@@ -2109,7 +2109,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
         <v>2</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
         <v>4</v>
       </c>
@@ -2149,14 +2149,14 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="30" t="s">
         <v>28</v>
       </c>
@@ -2166,7 +2166,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
         <v>2</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
         <v>4</v>
       </c>
@@ -2206,14 +2206,14 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="30" t="s">
         <v>29</v>
       </c>
@@ -2223,7 +2223,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32" t="s">
         <v>2</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>26.96</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
         <v>4</v>
       </c>
@@ -2263,14 +2263,14 @@
         <v>23.15</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="30" t="s">
         <v>30</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="32" t="s">
         <v>2</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="32" t="s">
         <v>4</v>
       </c>
